--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_biobio.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2021_biobio.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>21.91173880886134</v>
+      </c>
+      <c r="C2">
         <v>33.2215686965097</v>
-      </c>
-      <c r="C2">
-        <v>21.91173880886134</v>
       </c>
       <c r="D2">
         <v>3.010092657379726</v>
       </c>
       <c r="E2">
-        <v>21.41485231684337</v>
+        <v>14.12445796535519</v>
       </c>
       <c r="F2">
         <v>64.46068971780143</v>
       </c>
       <c r="G2">
-        <v>14.12445796535519</v>
+        <v>21.41485231684337</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.87921884950116</v>
+      </c>
+      <c r="C3">
         <v>29.00923370834218</v>
-      </c>
-      <c r="C3">
-        <v>28.87921884950116</v>
       </c>
       <c r="D3">
         <v>3.447178267630111</v>
       </c>
       <c r="E3">
-        <v>18.37324594571885</v>
+        <v>18.2908999243761</v>
       </c>
       <c r="F3">
         <v>63.33585412990504</v>
       </c>
       <c r="G3">
-        <v>18.2908999243761</v>
+        <v>18.37324594571885</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>25.36862214143962</v>
+      </c>
+      <c r="C4">
         <v>33.19732180944786</v>
-      </c>
-      <c r="C4">
-        <v>25.36862214143962</v>
       </c>
       <c r="D4">
         <v>3.012291189451925</v>
       </c>
       <c r="E4">
-        <v>20.93597211500222</v>
+        <v>15.99878354036541</v>
       </c>
       <c r="F4">
         <v>63.06524434463237</v>
       </c>
       <c r="G4">
-        <v>15.99878354036541</v>
+        <v>20.93597211500222</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.58056765280072</v>
+      </c>
+      <c r="C5">
         <v>45.54737948640938</v>
-      </c>
-      <c r="C5">
-        <v>26.58056765280072</v>
       </c>
       <c r="D5">
         <v>2.195515990768216</v>
       </c>
       <c r="E5">
-        <v>26.4613505496423</v>
+        <v>15.44233118129471</v>
       </c>
       <c r="F5">
         <v>58.096318269063</v>
       </c>
       <c r="G5">
-        <v>15.44233118129471</v>
+        <v>26.4613505496423</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.7244276277817</v>
+      </c>
+      <c r="C6">
         <v>30.84717501442955</v>
-      </c>
-      <c r="C6">
-        <v>28.7244276277817</v>
       </c>
       <c r="D6">
         <v>3.241787941787942</v>
       </c>
       <c r="E6">
-        <v>19.33124346917451</v>
+        <v>18.00096455268869</v>
       </c>
       <c r="F6">
         <v>62.6677919781368</v>
       </c>
       <c r="G6">
-        <v>18.00096455268869</v>
+        <v>19.33124346917451</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>24.80467350010752</v>
+      </c>
+      <c r="C7">
         <v>37.53135975915705</v>
-      </c>
-      <c r="C7">
-        <v>24.80467350010752</v>
       </c>
       <c r="D7">
         <v>2.664438502673797</v>
       </c>
       <c r="E7">
-        <v>23.11954961916326</v>
+        <v>15.27983221106082</v>
       </c>
       <c r="F7">
         <v>61.60061816977591</v>
       </c>
       <c r="G7">
-        <v>15.27983221106082</v>
+        <v>23.11954961916326</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.31384904142646</v>
+      </c>
+      <c r="C8">
         <v>35.01139562944095</v>
-      </c>
-      <c r="C8">
-        <v>26.31384904142646</v>
       </c>
       <c r="D8">
         <v>2.856212904461038</v>
       </c>
       <c r="E8">
-        <v>21.70236635987784</v>
+        <v>16.31105478569796</v>
       </c>
       <c r="F8">
         <v>61.9865788544242</v>
       </c>
       <c r="G8">
-        <v>16.31105478569796</v>
+        <v>21.70236635987784</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>30.14382902773431</v>
+      </c>
+      <c r="C9">
         <v>24.27477023283845</v>
-      </c>
-      <c r="C9">
-        <v>30.14382902773431</v>
       </c>
       <c r="D9">
         <v>4.119503461446646</v>
       </c>
       <c r="E9">
-        <v>15.72010777786951</v>
+        <v>19.5208538168827</v>
       </c>
       <c r="F9">
         <v>64.75903840524779</v>
       </c>
       <c r="G9">
-        <v>19.5208538168827</v>
+        <v>15.72010777786951</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.60340196956133</v>
+      </c>
+      <c r="C10">
         <v>38.93240823634736</v>
-      </c>
-      <c r="C10">
-        <v>28.60340196956133</v>
       </c>
       <c r="D10">
         <v>2.568554182236275</v>
       </c>
       <c r="E10">
-        <v>23.23826063723198</v>
+        <v>17.07300781510921</v>
       </c>
       <c r="F10">
         <v>59.6887315476588</v>
       </c>
       <c r="G10">
-        <v>17.07300781510921</v>
+        <v>23.23826063723198</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.43527303735846</v>
+      </c>
+      <c r="C11">
         <v>37.62183867102749</v>
-      </c>
-      <c r="C11">
-        <v>25.43527303735846</v>
       </c>
       <c r="D11">
         <v>2.658030642107075</v>
       </c>
       <c r="E11">
-        <v>23.07279840594197</v>
+        <v>15.59899643190499</v>
       </c>
       <c r="F11">
         <v>61.32820516215304</v>
       </c>
       <c r="G11">
-        <v>15.59899643190499</v>
+        <v>23.07279840594197</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.87839015041524</v>
+      </c>
+      <c r="C12">
         <v>38.89889076020675</v>
-      </c>
-      <c r="C12">
-        <v>25.87839015041524</v>
       </c>
       <c r="D12">
         <v>2.570767393251717</v>
       </c>
       <c r="E12">
-        <v>23.60695026962253</v>
+        <v>15.70507172311705</v>
       </c>
       <c r="F12">
         <v>60.68797800726043</v>
       </c>
       <c r="G12">
-        <v>15.70507172311705</v>
+        <v>23.60695026962253</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>25.34035049248031</v>
+      </c>
+      <c r="C13">
         <v>35.24295086161212</v>
-      </c>
-      <c r="C13">
-        <v>25.34035049248031</v>
       </c>
       <c r="D13">
         <v>2.83744685263922</v>
       </c>
       <c r="E13">
-        <v>21.94683417542901</v>
+        <v>15.78019026810506</v>
       </c>
       <c r="F13">
         <v>62.27297555646592</v>
       </c>
       <c r="G13">
-        <v>15.78019026810506</v>
+        <v>21.94683417542901</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>27.50742379249743</v>
+      </c>
+      <c r="C14">
         <v>30.92539846069935</v>
-      </c>
-      <c r="C14">
-        <v>27.50742379249743</v>
       </c>
       <c r="D14">
         <v>3.233588085439937</v>
       </c>
       <c r="E14">
-        <v>19.51956546685537</v>
+        <v>17.36220020655625</v>
       </c>
       <c r="F14">
         <v>63.11823432658838</v>
       </c>
       <c r="G14">
-        <v>17.36220020655625</v>
+        <v>19.51956546685537</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>26.71685100298583</v>
+      </c>
+      <c r="C15">
         <v>30.21153118297658</v>
-      </c>
-      <c r="C15">
-        <v>26.71685100298583</v>
       </c>
       <c r="D15">
         <v>3.30999443207127</v>
       </c>
       <c r="E15">
-        <v>19.25179547647122</v>
+        <v>17.02486868903419</v>
       </c>
       <c r="F15">
         <v>63.72333583449458</v>
       </c>
       <c r="G15">
-        <v>17.02486868903419</v>
+        <v>19.25179547647122</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>30.6998056095529</v>
+      </c>
+      <c r="C16">
         <v>32.19013237063778</v>
-      </c>
-      <c r="C16">
-        <v>30.6998056095529</v>
       </c>
       <c r="D16">
         <v>3.106542056074766</v>
       </c>
       <c r="E16">
+        <v>18.84696255043474</v>
+      </c>
+      <c r="F16">
+        <v>61.39114621810537</v>
+      </c>
+      <c r="G16">
         <v>19.76189123145991</v>
-      </c>
-      <c r="F16">
-        <v>61.39114621810536</v>
-      </c>
-      <c r="G16">
-        <v>18.84696255043473</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.64185057165647</v>
+      </c>
+      <c r="C17">
         <v>37.38367455463973</v>
-      </c>
-      <c r="C17">
-        <v>26.64185057165647</v>
       </c>
       <c r="D17">
         <v>2.674964438122333</v>
       </c>
       <c r="E17">
-        <v>22.7913762360188</v>
+        <v>16.24250283676447</v>
       </c>
       <c r="F17">
         <v>60.96612092721673</v>
       </c>
       <c r="G17">
-        <v>16.24250283676447</v>
+        <v>22.7913762360188</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.3430147578858</v>
+      </c>
+      <c r="C18">
         <v>32.52392852091094</v>
-      </c>
-      <c r="C18">
-        <v>25.3430147578858</v>
       </c>
       <c r="D18">
         <v>3.074659321542476</v>
       </c>
       <c r="E18">
-        <v>20.60211456902216</v>
+        <v>16.0534018278478</v>
       </c>
       <c r="F18">
         <v>63.34448360313004</v>
       </c>
       <c r="G18">
-        <v>16.05340182784779</v>
+        <v>20.60211456902216</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>31.04677994545836</v>
+      </c>
+      <c r="C19">
         <v>28.20781763513041</v>
-      </c>
-      <c r="C19">
-        <v>31.04677994545836</v>
       </c>
       <c r="D19">
         <v>3.545116509667824</v>
       </c>
       <c r="E19">
-        <v>17.71240395170143</v>
+        <v>19.49506037321624</v>
       </c>
       <c r="F19">
         <v>62.79253567508233</v>
       </c>
       <c r="G19">
-        <v>19.49506037321624</v>
+        <v>17.71240395170143</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>32.32293360934496</v>
+      </c>
+      <c r="C20">
         <v>26.55626201389916</v>
-      </c>
-      <c r="C20">
-        <v>32.32293360934496</v>
       </c>
       <c r="D20">
         <v>3.765590200445434</v>
       </c>
       <c r="E20">
-        <v>16.7147510469986</v>
+        <v>20.34434620753839</v>
       </c>
       <c r="F20">
         <v>62.94090274546301</v>
       </c>
       <c r="G20">
-        <v>20.34434620753839</v>
+        <v>16.7147510469986</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>27.62664811069795</v>
+      </c>
+      <c r="C21">
         <v>28.76465087959641</v>
-      </c>
-      <c r="C21">
-        <v>27.62664811069795</v>
       </c>
       <c r="D21">
         <v>3.476489265195041</v>
       </c>
       <c r="E21">
-        <v>18.39274375576453</v>
+        <v>17.66508001983695</v>
       </c>
       <c r="F21">
         <v>63.94217622439852</v>
       </c>
       <c r="G21">
-        <v>17.66508001983695</v>
+        <v>18.39274375576453</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>26.61815396399847</v>
+      </c>
+      <c r="C22">
         <v>43.08693986978169</v>
-      </c>
-      <c r="C22">
-        <v>26.61815396399847</v>
       </c>
       <c r="D22">
         <v>2.320888888888889</v>
       </c>
       <c r="E22">
-        <v>25.38930264048747</v>
+        <v>15.68494696456782</v>
       </c>
       <c r="F22">
-        <v>58.9257503949447</v>
+        <v>58.92575039494471</v>
       </c>
       <c r="G22">
-        <v>15.68494696456782</v>
+        <v>25.38930264048748</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>26.13572343149808</v>
+      </c>
+      <c r="C23">
         <v>31.27272727272727</v>
-      </c>
-      <c r="C23">
-        <v>26.13572343149808</v>
       </c>
       <c r="D23">
         <v>3.197674418604651</v>
       </c>
       <c r="E23">
+        <v>16.60376130669617</v>
+      </c>
+      <c r="F23">
+        <v>63.52899069434503</v>
+      </c>
+      <c r="G23">
         <v>19.86724799895881</v>
-      </c>
-      <c r="F23">
-        <v>63.52899069434502</v>
-      </c>
-      <c r="G23">
-        <v>16.60376130669617</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.32126759586714</v>
+      </c>
+      <c r="C24">
         <v>36.904514250052</v>
-      </c>
-      <c r="C24">
-        <v>27.32126759586714</v>
       </c>
       <c r="D24">
         <v>2.709695603156708</v>
       </c>
       <c r="E24">
-        <v>22.47181522611156</v>
+        <v>16.636405860744</v>
       </c>
       <c r="F24">
         <v>60.89177891314446</v>
       </c>
       <c r="G24">
-        <v>16.636405860744</v>
+        <v>22.47181522611156</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.7010029818379</v>
+      </c>
+      <c r="C25">
         <v>35.29953917050691</v>
-      </c>
-      <c r="C25">
-        <v>26.7010029818379</v>
       </c>
       <c r="D25">
         <v>2.83289817232376</v>
       </c>
       <c r="E25">
-        <v>21.78976607208594</v>
+        <v>16.48204544693953</v>
       </c>
       <c r="F25">
         <v>61.72818848097454</v>
       </c>
       <c r="G25">
-        <v>16.48204544693953</v>
+        <v>21.78976607208594</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.37713836668077</v>
+      </c>
+      <c r="C26">
         <v>33.85722057667896</v>
-      </c>
-      <c r="C26">
-        <v>27.37713836668077</v>
       </c>
       <c r="D26">
         <v>2.953579717907516</v>
       </c>
       <c r="E26">
-        <v>20.99876279383646</v>
+        <v>16.97971731713718</v>
       </c>
       <c r="F26">
-        <v>62.02151988902635</v>
+        <v>62.02151988902636</v>
       </c>
       <c r="G26">
-        <v>16.97971731713718</v>
+        <v>20.99876279383647</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.65207170143991</v>
+      </c>
+      <c r="C27">
         <v>34.19042021745518</v>
-      </c>
-      <c r="C27">
-        <v>27.65207170143991</v>
       </c>
       <c r="D27">
         <v>2.924795874516545</v>
       </c>
       <c r="E27">
-        <v>21.12573763050385</v>
+        <v>17.08579210167953</v>
       </c>
       <c r="F27">
         <v>61.78847026781661</v>
       </c>
       <c r="G27">
-        <v>17.08579210167953</v>
+        <v>21.12573763050386</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>28.18220519369945</v>
+      </c>
+      <c r="C28">
         <v>50.53214133673903</v>
-      </c>
-      <c r="C28">
-        <v>28.18220519369945</v>
       </c>
       <c r="D28">
         <v>1.97893850042123</v>
       </c>
       <c r="E28">
+        <v>15.76941400666984</v>
+      </c>
+      <c r="F28">
+        <v>55.95521676989042</v>
+      </c>
+      <c r="G28">
         <v>28.27536922343973</v>
-      </c>
-      <c r="F28">
-        <v>55.95521676989043</v>
-      </c>
-      <c r="G28">
-        <v>15.76941400666984</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>26.19173262972735</v>
+      </c>
+      <c r="C29">
         <v>43.14863676341249</v>
-      </c>
-      <c r="C29">
-        <v>26.19173262972735</v>
       </c>
       <c r="D29">
         <v>2.317570322054627</v>
       </c>
       <c r="E29">
-        <v>25.4804196530591</v>
+        <v>15.46691596551366</v>
       </c>
       <c r="F29">
         <v>59.05266438142723</v>
       </c>
       <c r="G29">
-        <v>15.46691596551366</v>
+        <v>25.4804196530591</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.5153458543289</v>
+      </c>
+      <c r="C30">
         <v>43.74713696747595</v>
-      </c>
-      <c r="C30">
-        <v>25.5153458543289</v>
       </c>
       <c r="D30">
         <v>2.28586387434555</v>
       </c>
       <c r="E30">
-        <v>25.84573748308525</v>
+        <v>15.0744248985115</v>
       </c>
       <c r="F30">
         <v>59.07983761840325</v>
       </c>
       <c r="G30">
-        <v>15.0744248985115</v>
+        <v>25.84573748308526</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>27.6460578559274</v>
+      </c>
+      <c r="C31">
         <v>36.58536585365854</v>
-      </c>
-      <c r="C31">
-        <v>27.6460578559274</v>
       </c>
       <c r="D31">
         <v>2.733333333333333</v>
       </c>
       <c r="E31">
-        <v>22.27671478897561</v>
+        <v>16.8335981211577</v>
       </c>
       <c r="F31">
-        <v>60.88968708986668</v>
+        <v>60.88968708986669</v>
       </c>
       <c r="G31">
-        <v>16.8335981211577</v>
+        <v>22.27671478897562</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>25.99038974906567</v>
+      </c>
+      <c r="C32">
         <v>39.1884676988788</v>
-      </c>
-      <c r="C32">
-        <v>25.99038974906567</v>
       </c>
       <c r="D32">
         <v>2.551771117166213</v>
       </c>
       <c r="E32">
-        <v>23.72486909302476</v>
+        <v>15.7346951968453</v>
       </c>
       <c r="F32">
         <v>60.54043571012994</v>
       </c>
       <c r="G32">
-        <v>15.7346951968453</v>
+        <v>23.72486909302476</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>25.51577669902913</v>
+      </c>
+      <c r="C33">
         <v>44.63743932038835</v>
-      </c>
-      <c r="C33">
-        <v>25.51577669902913</v>
       </c>
       <c r="D33">
         <v>2.240271877655055</v>
       </c>
       <c r="E33">
-        <v>26.23367360584853</v>
+        <v>14.99576516738733</v>
       </c>
       <c r="F33">
         <v>58.77056122676414</v>
       </c>
       <c r="G33">
-        <v>14.99576516738733</v>
+        <v>26.23367360584853</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>35.78193578193578</v>
+      </c>
+      <c r="C34">
         <v>22.17602217602218</v>
-      </c>
-      <c r="C34">
-        <v>35.78193578193578</v>
       </c>
       <c r="D34">
         <v>4.509375</v>
       </c>
       <c r="E34">
-        <v>14.03919274641708</v>
+        <v>22.6528224627084</v>
       </c>
       <c r="F34">
         <v>63.30798479087453</v>
       </c>
       <c r="G34">
-        <v>22.6528224627084</v>
+        <v>14.03919274641708</v>
       </c>
     </row>
   </sheetData>
